--- a/survey_templates/045_holiday_celebration_guessing_poll--survey_templates.xlsx
+++ b/survey_templates/045_holiday_celebration_guessing_poll--survey_templates.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,19 +520,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>snow_count_1</t>
+          <t>participant_info_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Participant Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -537,19 +543,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>snow_count_2</t>
+          <t>nyc_snowfall_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Snowfall in New York City, USA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -564,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>snow_count_3</t>
+          <t>tokyo_snowfall_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Snowfall in Tokyo, Japan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -591,19 +589,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>snow_count_4</t>
+          <t>paris_snowfall_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Snowfall in Paris, France</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -618,19 +612,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>snow_count_5</t>
+          <t>favorite_snow_destination_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Favorite Winter Destination</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -645,19 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>snow_count_6</t>
+          <t>visits_to_snow_destination_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Times visited favorite snow destination</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -672,19 +658,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>snow_count_7</t>
+          <t>favorite_activity_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
+          <t>Favorite Winter Activity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,25 +676,182 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Month with most snowfall in hometown</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>snow_count_8</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>How many snowflakes will fall in December?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Give your prediction</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>hometown_snowfall_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Snowfall in hometown in December</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>favorite_holiday_tradition_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Favorite Holiday Tradition related to snowfall</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>number_of_snowshoes_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Number of snowshoes owned</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>most_snowfall_region_1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Region with most snowfall</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>least_snowfall_region_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Region with least snowfall</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nyc_snowfall_2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nyc Snowfall 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>time_of_day_1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Time of day to go outside when it's snowing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -724,6 +863,433 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>january</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>february</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>march</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>april</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>june</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>august</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>september</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>october</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>november</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>december</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>month_with_most_snowfall_1_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>most_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>north_america</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>most_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>south_america</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>most_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>europe</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>most_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>most_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>africa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>least_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>north_america</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>least_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>south_america</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>least_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>europe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>least_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>least_snowfall_region_1_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>africa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
